--- a/Result/profitability/3035.xlsx
+++ b/Result/profitability/3035.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.63</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7212500000000001</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>38.20999999999999</v>
+        <v>38.065</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6475</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>38.07</v>
+        <v>38.36625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0.61375</v>
+        <v>0.5425</v>
       </c>
       <c r="N4" t="n">
-        <v>38.28125</v>
+        <v>41.39875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.49</v>
+        <v>0.5725</v>
       </c>
       <c r="N5" t="n">
-        <v>42.32875</v>
+        <v>44.95874999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.49875</v>
+        <v>0.5212500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>45.535</v>
+        <v>47.03625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0.52</v>
+        <v>0.515</v>
       </c>
       <c r="N7" t="n">
-        <v>46.9575</v>
+        <v>47.34</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0.52</v>
+        <v>0.5650000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>47.05</v>
+        <v>46.79</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.5525</v>
       </c>
       <c r="N11" t="n">
-        <v>45.72499999999999</v>
+        <v>45.725</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3314</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1815</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F75" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>271</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.17%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>111</v>
+      </c>
+      <c r="J75" t="n">
+        <v>382</v>
+      </c>
+      <c r="K75" t="n">
+        <v>198</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>37.6975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.079999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04397463002114166</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.8701406120760959</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
